--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_02_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_02_19_Cau.xlsx
@@ -645,7 +645,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh đơn vị mà `split()` đếm với đơn vị mà mô hình xử lý.</t>
+          <t>Dùng `tokenizer.encode()` chính xác hơn `len(text.split())` vì tokenizer sử dụng đúng từ điển và thuật toán tách mảnh từ (BPE/WordPiece) của mô hình, đếm chính xác số đơn vị token mà mô hình thực sự nhận.</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh nhóm nào có kết quả đa dạng hơn dựa trên đầu ra quan sát được.</t>
+          <t>Khi chỉ temperature thay đổi, nhóm Y đa dạng hơn và có câu lạc đề chứng tỏ nhóm Y được chạy với temperature cao hơn nhóm X (temperature cao làm phẳng phân phối xác suất và tăng tính ngẫu nhiên).</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dừng ở token làm tổng xác suất tích lũy lần đầu đạt hoặc vượt ngưỡng.</t>
+          <t>Các token sắp xếp giảm dần: K = 0,50; L = 0,20; M = 0,15... Với top-p = 0,68, tổng tích lũy: K = 0,50 (&lt; 0,68); K + L = 0,70 (&gt;= 0,68). Vậy tập nhỏ nhất được giữ lại gồm {K, L}.</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hình dung tổng xác suất tích lũy sẽ đạt ngưỡng sớm hay muộn khi top-p nhỏ đi.</t>
+          <t>Khi giảm top-p từ 0,95 xuống 0,60, tổng xác suất tích lũy của các token có xác suất cao nhất đạt ngưỡng 0,60 sớm hơn, khiến tập token ứng viên được giữ lại trở nên hẹp hơn.</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
@@ -992,7 +996,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chia ngân sách đầu ra cho số bản tóm tắt độc lập.</t>
+          <t>Ngân sách tối đa 2.400 token đầu ra chia đều cho 12 bản tóm tắt độc lập: 2.400 / 12 = 200 token cho mỗi bản.</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1042,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt cấu hình trước khi gọi với thông tin cho biết lý do dừng sau khi nhận phản hồi.</t>
+          <t>Khi đặt `max_output_tokens=120` và phản hồi bị dừng giữa câu, có thể mô hình đã chạm giới hạn đầu ra; cần kiểm tra `finish_reason` trong phản hồi (nếu là 'length' thì khẳng định bị cắt do hết token).</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1181,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -1191,7 +1199,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cộng mọi thành phần trước rồi lấy dung lượng cửa sổ trừ đi tổng đó.</t>
+          <t>Tổng số token đã phân bổ gồm lời nhắc (2.500), lịch sử hội thoại (8.500), ngữ cảnh truy xuất (12.000) và giới hạn đầu ra (6.000) là: 2.500 + 8.500 + 12.000 + 6.000 = 29.000 token. Số token còn dư trong cửa sổ ngữ cảnh 32.000 là: 32.000 - 29.000 = 3.000 token.</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1252,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính phần vượt trước, rồi loại các phương án làm mất phần bằng chứng phải giữ.</t>
+          <t>Tổng ngân sách hiện tại = 2.000 (prompt) + 6.000 (history) + 7.000 (evidence) + 4.000 (output) = 19.000 token, vượt cửa sổ 16.000 là 3.000 token. Giảm giới hạn đầu ra 2.000 token và tóm tắt giảm lịch sử 1.000 token giúp giảm đúng 3.000 token vừa vặn cửa sổ mà vẫn giữ nguyên bằng chứng 7.000.</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1379,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm dấu hiệu cho thấy câu trả lời có thể đã thay đổi sau thời điểm mô hình được huấn luyện.</t>
+          <t>Giá API và endpoint thay đổi theo thời gian thực và không thể trả lời chính xác từ trí nhớ tĩnh của mô hình; cách xử lý đúng là tra cứu tài liệu chính thức hiện hành hoặc gọi tool tìm kiếm và ghi rõ mốc thời gian kiểm tra.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_02_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_02_19_Cau.xlsx
@@ -678,10 +678,15 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tên mô hình gửi trong yêu cầu và tên mô hình dùng để chọn cách mã hóa phải nhất quán.
-Phân tích theo nguyên lý thiết kế: Tên mô hình gửi trong yêu cầu và tên mô hình dùng để chọn cách mã hóa phải nhất quán.</t>
+- Xác định đúng bản chất lỗi (1.5 điểm): Nêu rõ lỗi Tokenizer Mismatch do gọi bộ mã hóa không tương thích giữa alpha-chat và beta-chat.
+- Trả về chính xác số token hợp lệ (1.5 điểm): Xác định đúng số token phải trả về là 11 token.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Lỗi kỹ thuật: Lỗi Tokenizer Mismatch (không đồng nhất bộ mã hóa token giữa thư viện client và mô hình runtime). Dự án gửi request cho mô hình `alpha-chat` nhưng hàm đếm token lại khởi tạo bộ mã hóa của mô hình `beta-chat` (`encoding_for_model('beta-chat')`). Mỗi dòng mô hình có tập từ vựng (vocabulary), quy tắc phân tách regex và cơ chế ghép byte khác nhau, dẫn đến việc đếm sai lệch số lượng token thực tế mà server mô hình nhận được.
+- Số token đúng phải trả về: Chính xác 11 token (kết quả mã hóa tương ứng với mô hình `alpha-chat` thực sự phục vụ request).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tính nhất quán giữa client-side token counting và server-side model tokenizer là nguyên tắc bắt buộc để kiểm soát chi phí và ngăn ngừa lỗi tràn context window. Việc ước lượng thấp hơn thực tế (đếm ra 9 nhưng server tính 11) có thể khiến hệ thống bị từ chối phục vụ (HTTP 400 Bad Request) khi prompt tiến sát giới hạn ngữ cảnh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Tiktoken Library Documentation - OpenAI. https://github.com/openai/tiktoken; OpenAI Cookbook - How to count tokens with tiktoken (https://cookbook.openai.com/examples/how_to_count_tokens_with_tiktoken)</t>
         </is>
       </c>
     </row>
@@ -802,10 +807,15 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đổi tham số theo hướng làm phân phối xác suất bớt tập trung, rồi nêu cái giá của sự biến thiên cao hơn.
-Phân tích theo nguyên lý thiết kế: Đổi tham số theo hướng làm phân phối xác suất bớt tập trung, rồi nêu cái giá của sự biến thiên cao hơn.</t>
+- Đề xuất đúng hướng tham số (1.5 điểm): Khẳng định tăng temperature và giải thích cơ chế làm phẳng phân phối xác suất softmax để tăng tính đa dạng.
+- Nhận diện đúng rủi ro kỹ thuật (1.5 điểm): Nêu rõ rủi ro mất mạch lạc, ảo giác hoặc câu văn vô nghĩa, chệch hướng yêu cầu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Hướng thay đổi temperature: Cần TĂNG giá trị `temperature` (ví dụ từ mức thấp ~0.0 - 0.2 lên mức ~0.7 - 0.9 hoặc 1.0). Khi tăng temperature, phân phối xác suất softmax trên toàn bộ từ vựng bị làm phẳng (flattened distribution), làm giảm độ chênh lệch xác suất giữa token đứng đầu và các token đứng sau, kích thích mô hình khám phá các từ ngữ và cấu trúc câu mới mẻ, phá vỡ sự rập khuôn lặp lại.
+- Rủi ro cần theo dõi: Nguy cơ xuất hiện ảo giác (hallucination), câu văn mất tính mạch lạc/ngữ pháp (syntactic incoherence), hoặc slogan đi chệch khỏi tông giọng thương hiệu, trở nên kỳ dị hoặc vô nghĩa (unconstrained generation).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Temperature ($T$) là tham số điều tiết độ entropy trong hàm softmax: $P(w_i) = \frac{\exp(z_i / T)}{\sum_j \exp(z_j / T)}$. Khi $T$ thấp, mô hình tiến gần về greedy decoding gây lặp từ; tăng $T$ giúp tăng tính đa dạng sáng tạo (diversity), nhưng cần kết hợp với các bộ lọc hậu xử lý hoặc tham số `top_p` để kiểm soát chất lượng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Holtzman, A., et al. (2020). The Curious Case of Neural Text Degeneration (Nucleus Sampling). ICLR 2020. https://arxiv.org/abs/1904.09751; OpenAI API Reference - Sampling Parameters.</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1133,15 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm chuỗi ký tự phân cách hai bản ghi.
-Phân tích theo nguyên lý thiết kế: Tìm chuỗi ký tự phân cách hai bản ghi.</t>
+- Xác định đúng stop sequence (1.5 điểm): Chỉ định chính xác chuỗi dừng `"&lt;END_RECORD&gt;"`.
+- Xác định đúng đầu ra giữ lại (1.5 điểm): Nêu đúng kết quả thu được là `"Lan|8"` và giải thích việc ngăn chặn phần bản ghi thừa phía sau.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Stop sequence cần thiết lập: `["&lt;END_RECORD&gt;"]` (truyền chuỗi ký tự `"&lt;END_RECORD&gt;"` vào tham số `stop` của API gọi mô hình).
+- Phần đầu ra được giữ lại: `"Lan|8"` (mô hình sẽ ngắt quá trình autoregressive decoding ngay khi chuẩn bị sinh token của `"&lt;END_RECORD&gt;"`; chuỗi dừng bị loại bỏ khỏi output trả về và toàn bộ phần bản ghi phía sau `"Minh|9"` hoàn toàn không bị sinh ra, giúp tối ưu tối đa chi phí và độ trễ).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Stop sequence là cơ chế can thiệp sớm tại cấp độ sinh token (token-level early stopping). Thay vì để mô hình sinh toàn bộ chuỗi rồi dùng regex cắt chuỗi ở tầng backend, việc thiết lập stop sequence tại runtime của LLM giúp tiết kiệm token đầu ra (completion tokens) và giảm độ trễ Time-to-Last-Token (TTLT).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI API Reference - Stop Sequences (https://platform.openai.com/docs/api-reference/chat/create#chat-create-stop); Anthropic Claude Messages API - Stop Sequences.</t>
         </is>
       </c>
     </row>
@@ -1162,10 +1177,21 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Lập một phép tính gồm lời nhắc + lịch sử hội thoại + ngữ cảnh truy xuất + giới hạn đầu ra.
-Phân tích theo nguyên lý thiết kế: Lập một phép tính gồm lời nhắc + lịch sử hội thoại + ngữ cảnh truy xuất + giới hạn đầu ra.</t>
+- Tính tổng tải và kết luận tính khả thi (1.5 điểm): Thiết lập phép tính 3.000 + 24.000 + 70.000 + 40.000 = 137.000 token và kết luận không vừa (vượt ngưỡng 128.000).
+- Tính chính xác lượng token đầu vào cần giảm (1.5 điểm): Tính đúng cần giảm tối thiểu 9.000 token đầu vào (giữ đầu vào &lt;= 88.000 token).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định lần gọi có vừa cửa sổ ngữ cảnh không:
+- Tổng token đầu vào = Lời nhắc (3.000) + Lịch sử hội thoại (24.000) + Ngữ cảnh truy xuất (70.000) = 97.000 token.
+- Tổng tải yêu cầu của lần gọi = Token đầu vào (97.000) + Giới hạn đầu ra (40.000) = 137.000 token.
+- So sánh với giới hạn: 137.000 token &gt; 128.000 token (vượt quá 9.000 token).
+-&gt; Kết luận: Lần gọi này KHÔNG vừa cửa sổ ngữ cảnh (sẽ bị API từ chối với lỗi HTTP 400 ContextWindowExceeded).
+2. Số token đầu vào tối thiểu cần giảm:
+- Để giữ nguyên giới hạn đầu ra 40.000 token trong dung lượng 128.000 token, ngân sách tối đa dành cho đầu vào là: 128.000 - 40.000 = 88.000 token.
+- Số token đầu vào tối thiểu cần giảm là: 97.000 - 88.000 = 9.000 token.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Cửa sổ ngữ cảnh của LLM là giới hạn cứng áp dụng cho tổng của cả chuỗi đầu vào và chuỗi đầu ra: $L_{input} + L_{max\_output} \le L_{context\_window}$. Trong kiến trúc RAG quy mô lớn, bộ quản lý ngữ cảnh (Context Window Budgeter) bắt buộc phải thực hiện cắt tỉa (pruning) hoặc nén ngữ cảnh truy xuất trước khi dispatch request đến model.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Documentation - Managing context limits (https://platform.openai.com/docs/guides/text-generation); Anthropic Claude Documentation - Context Window Limits.</t>
         </is>
       </c>
     </row>
@@ -1330,10 +1356,15 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giảm phần không liên quan nhưng đừng biến bằng chứng thành một kết luận không còn truy được nguồn.
-Phân tích theo nguyên lý thiết kế: Giảm phần không liên quan nhưng đừng biến bằng chứng thành một kết luận không còn truy được nguồn.</t>
+- Đề xuất tổ chức thông tin (1.5 điểm): Nêu giải pháp chia nhỏ (chunking/RAG) và sắp xếp vị trí ưu tiên đầu/cuối để tránh hiện tượng Lost in the Middle.
+- Thông tin kiểm chứng bắt buộc (1.5 điểm): Nêu rõ trích dẫn nguyên văn, số điều khoản, số trang/mục và phiên bản tài liệu để truy vết nguồn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đề xuất thay đổi về cách truy xuất / tổ chức thông tin: Thay vì gửi nguyên văn 400 trang theo thứ tự gốc, cần áp dụng RAG phân đoạn (chunking thành các đoạn nhỏ 500-1000 token có cấu trúc) kết hợp bộ lọc metadata và re-ranking. Nếu cần gửi nhiều đoạn ngữ cảnh, phải đặt điều khoản trọng yếu nhất lên đầu hoặc xuống cuối prompt nhằm khắc phục hiện tượng 'Lost in the Middle' (mô hình chú ý kém ở giữa ngữ cảnh dài).
+2. Thông tin phải giữ để câu trả lời kiểm chứng được: Bắt buộc phải giữ lại trích dẫn nguyên văn điều khoản (verbatim quote), số hiệu điều/khoản/chương, tiêu đề mục, số trang trong tài liệu gốc và phiên bản/ngày ban hành của chính sách.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Hiện tượng 'Lost in the Middle' chứng minh sự suy giảm hiệu quả chú ý của cơ chế Self-Attention khi thông tin nằm sâu giữa ngữ cảnh khổng lồ. Thiết kế hệ thống thông minh đòi hỏi phải tinh lọc ngữ cảnh tập trung (high signal-to-noise ratio) và bảo toàn siêu dữ liệu truy vết nguồn gốc (provenance metadata) để người dùng và hệ thống audit có thể đối chiếu độ tin cậy.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Liu, N. F., et al. (2023). Lost in the Middle: How Language Models Use Long Contexts. TACL 2024. https://arxiv.org/abs/2307.03172; LangChain RAG Architecture Guide.</t>
         </is>
       </c>
     </row>
@@ -1408,10 +1439,18 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Câu trả lời cần cả bước lấy dữ kiện mới và cách nói rõ độ mới của dữ kiện.
-Phân tích theo nguyên lý thiết kế: Câu trả lời cần cả bước lấy dữ kiện mới và cách nói rõ độ mới của dữ kiện.</t>
+- Bước nhận diện ranh giới tri thức (1.0 điểm): Nhận diện câu hỏi vượt cutoff và từ chối suy đoán chủ quan.
+- Bước truy xuất công cụ thời gian thực (1.0 điểm): Nêu rõ việc gọi tool search/API để lấy dữ liệu mới nhất.
+- Bước phản hồi có neo thời gian và nguồn (1.0 điểm): Trình bày câu trả lời kèm mốc thời gian cụ thể và dẫn nguồn đối chiếu minh bạch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Quy trình trả lời an toàn gồm 3 bước:
+1. Kiểm tra giới hạn tri thức (Knowledge Cutoff Check): Nhận diện truy vấn yêu cầu dữ kiện mang tính biến động thời gian thực (chức vụ lãnh đạo hiện tại) vượt ngoài mốc cutoff của trọng số tĩnh; không tự suy đoán dựa trên dữ liệu huấn luyện cũ.
+2. Kích hoạt truy xuất dữ liệu ngoài (Real-time Tool Retrieval): Gọi công cụ tìm kiếm web (Web Search tool) hoặc cơ sở dữ liệu doanh nghiệp chính thức với truy vấn có chứa mốc thời gian hiện tại để lấy thông cáo báo chí, hồ sơ quản trị mới nhất của công ty X.
+3. Phản hồi kèm mốc thời gian và trích dẫn nguồn (Time-grounded Response with Citation): Tổng hợp câu trả lời nêu rõ: 'Tính đến ngày DD/MM/YYYY theo nguồn [Tên cơ quan/báo chí], CEO hiện tại của công ty X là Ông/Bà Y', kèm đường dẫn nguồn để người dùng đối chiếu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc Grounding &amp; Temporal Anchoring đòi hỏi LLM phải nhận thức được ranh giới tri thức đóng (parametric knowledge cutoff). Đối với thông tin thời gian thực, câu trả lời bắt buộc phải được neo vào bằng chứng truy xuất động và công khai ngày tháng kiểm chứng để ngăn ngừa rủi ro thông tin lỗi thời.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Documentation - Retrieval and Web Browsing Best Practices (https://platform.openai.com/docs/guides/prompt-engineering); Google Search Grounding for Gemini API.</t>
         </is>
       </c>
     </row>
